--- a/out/MLP-Mamba1_repeat_2_000007.xlsx
+++ b/out/MLP-Mamba1_repeat_2_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.791318200473973</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.791318200473973</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.791318200473973</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.4867320633075706</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.191318200473974</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.4867320633075706</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.791318200473973</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.791318200473973</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.4867320633075706</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.791318200473973</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0003128606662441743</v>
+        <v>-0.0002394861812497256</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.606821416216207</v>
+        <v>2.760921971396211</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC40" t="n">
-        <v>7.219218327423347</v>
+        <v>5.526111829900075</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.5408589378922931</v>
+        <v>0.4140125427739168</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.4867320633075706</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.689273981957561</v>
+        <v>3.589509452425944</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.6762496564827519</v>
+        <v>0.517650446177626</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC42" t="n">
-        <v>5.501000317404898</v>
+        <v>4.21086350471284</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.9694006755205329</v>
+        <v>0.7420494596892927</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.191318200473974</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC43" t="n">
-        <v>6.763933861762538</v>
+        <v>5.177604110972209</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>1.037066704129531</v>
+        <v>0.7938459368700677</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.791318200473973</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC44" t="n">
-        <v>7.868739242599826</v>
+        <v>6.023301850896911</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.099081675901849</v>
+        <v>0.8413159482763287</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.791318200473973</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC45" t="n">
-        <v>9.02991514564512</v>
+        <v>6.912149357504775</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4959957846247486</v>
+        <v>0.379670905874038</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.791318200473973</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC46" t="n">
-        <v>8.921910229767317</v>
+        <v>6.829474614046627</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2395432937219287</v>
+        <v>0.1833630509307309</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC47" t="n">
-        <v>8.904612104116666</v>
+        <v>6.816233383465289</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1141346349051183</v>
+        <v>0.08736703470296096</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC48" t="n">
-        <v>8.893149076341546</v>
+        <v>6.807458725632082</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03381765937328369</v>
+        <v>0.02588624295656222</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.191318200473974</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC49" t="n">
-        <v>8.84652695813543</v>
+        <v>6.771770614288536</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02236912059739604</v>
+        <v>0.0171232648820775</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.791318200473973</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC50" t="n">
-        <v>8.857429882367343</v>
+        <v>6.780116658058981</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01144725361182644</v>
+        <v>0.008761056141228773</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC51" t="n">
-        <v>8.857940148676706</v>
+        <v>6.780506088177949</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005852766977881172</v>
+        <v>0.004479679822385395</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC52" t="n">
-        <v>8.858192623681276</v>
+        <v>6.780698192468043</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.00219753510900249</v>
+        <v>0.00168058271056651</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC53" t="n">
-        <v>8.856729481613208</v>
+        <v>6.779577037790871</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001195383696911266</v>
+        <v>0.0009140566586660831</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC54" t="n">
-        <v>8.856921486927247</v>
+        <v>6.779722872100039</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005727686740559047</v>
+        <v>0.000437664582460989</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.191318200473974</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC55" t="n">
-        <v>8.856871676763305</v>
+        <v>6.779683563465503</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003531596627463547</v>
+        <v>0.0002685395226469412</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.4867320633075706</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC56" t="n">
-        <v>8.857004162142534</v>
+        <v>6.779783755487863</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001823451866623522</v>
+        <v>0.0001380823128904778</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC57" t="n">
-        <v>8.85701548475947</v>
+        <v>6.779791267130939</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>8.591747490145118e-05</v>
+        <v>6.493651915496244e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.191318200473974</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC58" t="n">
-        <v>8.857004857235333</v>
+        <v>6.779781938266217</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.256158699932203e-05</v>
+        <v>3.97701232216949e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC59" t="n">
-        <v>8.857025302832854</v>
+        <v>6.779796511205625</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.180905938564374e-05</v>
+        <v>1.481539171982363e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC60" t="n">
-        <v>8.857015041371366</v>
+        <v>6.779787508627801</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>6.323060732339969e-06</v>
+        <v>4.264322417369065e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC61" t="n">
-        <v>8.857006890260344</v>
+        <v>6.779780042050807</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>1.675769385467227e-06</v>
+        <v>-5.494870763551826e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC62" t="n">
-        <v>8.857002882454433</v>
+        <v>6.779775786872636</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC63" t="n">
-        <v>8.856997015011748</v>
+        <v>6.779770064593606</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>2.791318200473973</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC64" t="n">
-        <v>8.856991945656379</v>
+        <v>6.779764995238237</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.791318200473973</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC65" t="n">
-        <v>8.856987580682413</v>
+        <v>6.779760630264268</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.791318200473973</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC66" t="n">
-        <v>8.856988671928868</v>
+        <v>6.779761721510726</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC67" t="n">
-        <v>8.856987982321732</v>
+        <v>6.779761031903589</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC68" t="n">
-        <v>8.856988012634133</v>
+        <v>6.779761062215991</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.191318200473974</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC69" t="n">
-        <v>8.856987823181624</v>
+        <v>6.779760872763481</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.791318200473973</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC70" t="n">
-        <v>8.856987876228327</v>
+        <v>6.779760925810185</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC71" t="n">
-        <v>8.856987929275029</v>
+        <v>6.779760978856887</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC72" t="n">
-        <v>8.856987891384527</v>
+        <v>6.779760940966384</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC73" t="n">
-        <v>8.856987762556821</v>
+        <v>6.779760812138678</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC74" t="n">
-        <v>8.856987618572914</v>
+        <v>6.77976066815477</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC75" t="n">
-        <v>8.856987459432805</v>
+        <v>6.779760509014662</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC76" t="n">
-        <v>8.856987512479508</v>
+        <v>6.779760562061365</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC77" t="n">
-        <v>8.856987459432805</v>
+        <v>6.779760509014662</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC78" t="n">
-        <v>8.856987459432805</v>
+        <v>6.779760509014662</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>2.791318200473973</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC79" t="n">
-        <v>8.856987277558396</v>
+        <v>6.779760327140253</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.791318200473973</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC80" t="n">
-        <v>8.856987444276605</v>
+        <v>6.779760493858461</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC81" t="n">
-        <v>8.856987641307214</v>
+        <v>6.779760690889072</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC82" t="n">
-        <v>8.856987482167106</v>
+        <v>6.779760531748964</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.791318200473973</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC83" t="n">
-        <v>8.856987520057608</v>
+        <v>6.779760569639465</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC84" t="n">
-        <v>8.856987717088218</v>
+        <v>6.779760766670075</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC85" t="n">
-        <v>8.856987694353917</v>
+        <v>6.779760743935774</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC86" t="n">
-        <v>8.856987542791909</v>
+        <v>6.779760592373766</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC87" t="n">
-        <v>8.856987467010907</v>
+        <v>6.779760516592763</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC88" t="n">
-        <v>8.856987565526209</v>
+        <v>6.779760615108068</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.791318200473973</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC89" t="n">
-        <v>8.856987573104311</v>
+        <v>6.779760622686168</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC90" t="n">
-        <v>8.856987838337824</v>
+        <v>6.779760887919682</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.791318200473973</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC91" t="n">
-        <v>8.856987542791909</v>
+        <v>6.779760592373766</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.791318200473973</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC92" t="n">
-        <v>8.856987785291123</v>
+        <v>6.779760834872978</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC93" t="n">
-        <v>8.856987868650226</v>
+        <v>6.779760918232084</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.791318200473973</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC94" t="n">
-        <v>8.856987701932017</v>
+        <v>6.779760751513875</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC95" t="n">
-        <v>8.856987891384527</v>
+        <v>6.779760940966384</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC96" t="n">
-        <v>8.856987542791909</v>
+        <v>6.779760592373766</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC97" t="n">
-        <v>8.856987338183199</v>
+        <v>6.779760387765055</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC98" t="n">
-        <v>8.856987451854703</v>
+        <v>6.779760501436561</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC99" t="n">
-        <v>8.856987467010907</v>
+        <v>6.779760516592763</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC100" t="n">
-        <v>8.856987232089793</v>
+        <v>6.779760281671651</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC101" t="n">
-        <v>8.856987292714596</v>
+        <v>6.779760342296453</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC102" t="n">
-        <v>8.85698716388689</v>
+        <v>6.779760213468746</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.791318200473973</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC103" t="n">
-        <v>8.856987300292698</v>
+        <v>6.779760349874554</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.4867320633075706</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC104" t="n">
-        <v>8.856987474589005</v>
+        <v>6.779760524170863</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC105" t="n">
-        <v>8.856987618572914</v>
+        <v>6.77976066815477</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC106" t="n">
-        <v>8.856987451854703</v>
+        <v>6.779760501436561</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC107" t="n">
-        <v>8.856987444276605</v>
+        <v>6.779760493858461</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC108" t="n">
-        <v>8.856987156308788</v>
+        <v>6.779760205890646</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.791318200473973</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC109" t="n">
-        <v>8.856987171464988</v>
+        <v>6.779760221046847</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC110" t="n">
-        <v>8.856987398808002</v>
+        <v>6.779760448389859</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.791318200473973</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC111" t="n">
-        <v>8.8569873836518</v>
+        <v>6.779760433233658</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC112" t="n">
-        <v>8.856987489745206</v>
+        <v>6.779760539327063</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4867320633075706</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC113" t="n">
-        <v>8.856987216933591</v>
+        <v>6.779760266515449</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC114" t="n">
-        <v>8.856987315448897</v>
+        <v>6.779760365030755</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC115" t="n">
-        <v>8.856987467010907</v>
+        <v>6.779760516592763</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC116" t="n">
-        <v>8.856987482167106</v>
+        <v>6.779760531748964</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC117" t="n">
-        <v>8.856987459432805</v>
+        <v>6.779760509014662</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC118" t="n">
-        <v>8.856987542791909</v>
+        <v>6.779760592373766</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC119" t="n">
-        <v>8.856987641307214</v>
+        <v>6.779760690889072</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC120" t="n">
-        <v>8.856987474589005</v>
+        <v>6.779760524170863</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC121" t="n">
-        <v>8.856987459432805</v>
+        <v>6.779760509014662</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC122" t="n">
-        <v>8.856987429120403</v>
+        <v>6.779760478702261</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC123" t="n">
-        <v>8.856987413964202</v>
+        <v>6.77976046354606</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC124" t="n">
-        <v>8.856987451854703</v>
+        <v>6.779760501436561</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC125" t="n">
-        <v>8.856987467010907</v>
+        <v>6.779760516592763</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC126" t="n">
-        <v>8.856987459432805</v>
+        <v>6.779760509014662</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_2_000007.xlsx
+++ b/out/MLP-Mamba1_repeat_2_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.3697952168820189</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.791318200473973</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.791318200473973</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.791318200473973</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.4867320633075706</v>
+        <v>0.3697952168820188</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-0.3794734148394769</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.1697952168820188</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.191318200473974</v>
+        <v>0.1697952168820188</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.1697952168820188</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.1697952168820188</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.791318200473973</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.791318200473973</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.4867320633075706</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.791318200473973</v>
+        <v>0.3697952168820188</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0003128606662441743</v>
+        <v>-0.0001281998857655562</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.606821416216207</v>
+        <v>1.477955268127638</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.4867320633075706</v>
+        <v>0.3697952168820188</v>
       </c>
       <c r="JC40" t="n">
-        <v>7.219218327423347</v>
+        <v>2.958195339930513</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.5408589378922931</v>
+        <v>0.2216260079729183</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.689273981957561</v>
+        <v>1.921508316968085</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.6762496564827519</v>
+        <v>0.2771045656649296</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.1697952168820188</v>
       </c>
       <c r="JC42" t="n">
-        <v>5.501000317404898</v>
+        <v>2.254126749657094</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.9694006755205329</v>
+        <v>0.397228080739525</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.191318200473974</v>
+        <v>0.9190638486035146</v>
       </c>
       <c r="JC43" t="n">
-        <v>6.763933861762538</v>
+        <v>2.771634940029304</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>1.037066704129531</v>
+        <v>0.4249553635384409</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.791318200473973</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC44" t="n">
-        <v>7.868739242599826</v>
+        <v>3.224347574305252</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.099081675901849</v>
+        <v>0.4503677693768257</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.791318200473973</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC45" t="n">
-        <v>9.02991514564512</v>
+        <v>3.700159209821334</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4959957846247486</v>
+        <v>0.2032425980310988</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.791318200473973</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC46" t="n">
-        <v>8.921910229767317</v>
+        <v>3.655902382679664</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2395432937219287</v>
+        <v>0.09815688533281568</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.4867320633075706</v>
+        <v>0.3697952168820189</v>
       </c>
       <c r="JC47" t="n">
-        <v>8.904612104116666</v>
+        <v>3.648814185345555</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1141346349051183</v>
+        <v>0.0467688335445853</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.1697952168820188</v>
       </c>
       <c r="JC48" t="n">
-        <v>8.893149076341546</v>
+        <v>3.644117016926645</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03381765937328369</v>
+        <v>0.0138565178037387</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.191318200473974</v>
+        <v>0.9190638486035146</v>
       </c>
       <c r="JC49" t="n">
-        <v>8.84652695813543</v>
+        <v>3.625012162686346</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02236912059739604</v>
+        <v>0.009163384353095005</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.791318200473973</v>
+        <v>0.9190638486035146</v>
       </c>
       <c r="JC50" t="n">
-        <v>8.857429882367343</v>
+        <v>3.629477587058327</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01144725361182644</v>
+        <v>0.004687481955047708</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.4867320633075706</v>
+        <v>0.1697952168820188</v>
       </c>
       <c r="JC51" t="n">
-        <v>8.857940148676706</v>
+        <v>3.62968373661017</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005852766977881172</v>
+        <v>0.002395889197842687</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC52" t="n">
-        <v>8.858192623681276</v>
+        <v>3.629784257088705</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.00219753510900249</v>
+        <v>0.0008972068212821196</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC53" t="n">
-        <v>8.856729481613208</v>
+        <v>3.629181719951207</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001195383696911266</v>
+        <v>0.0004867035624461271</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.1697952168820188</v>
       </c>
       <c r="JC54" t="n">
-        <v>8.856921486927247</v>
+        <v>3.629257485863503</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005727686740559047</v>
+        <v>0.0002318295252663819</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.191318200473974</v>
+        <v>0.1697952168820189</v>
       </c>
       <c r="JC55" t="n">
-        <v>8.856871676763305</v>
+        <v>3.629234100123648</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003531596627463547</v>
+        <v>0.000141609312497821</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.4867320633075706</v>
+        <v>0.3697952168820189</v>
       </c>
       <c r="JC56" t="n">
-        <v>8.857004162142534</v>
+        <v>3.629285567931942</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001823451866623522</v>
+        <v>7.220268681140886e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.4867320633075706</v>
+        <v>0.1697952168820188</v>
       </c>
       <c r="JC57" t="n">
-        <v>8.85701548475947</v>
+        <v>3.629287294285075</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>8.591747490145118e-05</v>
+        <v>3.196644583905158e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.191318200473974</v>
+        <v>0.1697952168820187</v>
       </c>
       <c r="JC58" t="n">
-        <v>8.857004857235333</v>
+        <v>3.629279975858463</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.256158699932203e-05</v>
+        <v>1.930378117749152e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.4867320633075706</v>
+        <v>0.3697952168820188</v>
       </c>
       <c r="JC59" t="n">
-        <v>8.857025302832854</v>
+        <v>3.629285601168426</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.180905938564374e-05</v>
+        <v>5.490501498730158e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC60" t="n">
-        <v>8.857015041371366</v>
+        <v>3.629278428664165</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>6.323060732339969e-06</v>
+        <v>1.468457874272584e-07</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC61" t="n">
-        <v>8.857006890260344</v>
+        <v>3.629272058343612</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>1.675769385467227e-06</v>
+        <v>-2.77474353817759e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC62" t="n">
-        <v>8.857002882454433</v>
+        <v>3.629267472434079</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.1697952168820188</v>
       </c>
       <c r="JC63" t="n">
-        <v>8.856997015011748</v>
+        <v>3.629262039302611</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>2.791318200473973</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC64" t="n">
-        <v>8.856991945656379</v>
+        <v>3.629256992681543</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.791318200473973</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC65" t="n">
-        <v>8.856987580682413</v>
+        <v>3.62925731096176</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.791318200473973</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC66" t="n">
-        <v>8.856988671928868</v>
+        <v>3.629258402208217</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.4867320633075706</v>
+        <v>0.3697952168820188</v>
       </c>
       <c r="JC67" t="n">
-        <v>8.856987982321732</v>
+        <v>3.62925771260108</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4867320633075706</v>
+        <v>0.3697952168820188</v>
       </c>
       <c r="JC68" t="n">
-        <v>8.856988012634133</v>
+        <v>3.629257742913483</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.191318200473974</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC69" t="n">
-        <v>8.856987823181624</v>
+        <v>3.629257553460973</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.791318200473973</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC70" t="n">
-        <v>8.856987876228327</v>
+        <v>3.629257606507676</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4867320633075706</v>
+        <v>0.3697952168820188</v>
       </c>
       <c r="JC71" t="n">
-        <v>8.856987929275029</v>
+        <v>3.629257659554378</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC72" t="n">
-        <v>8.856987891384527</v>
+        <v>3.629257621663876</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC73" t="n">
-        <v>8.856987762556821</v>
+        <v>3.629257492836169</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC74" t="n">
-        <v>8.856987618572914</v>
+        <v>3.629257348852262</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC75" t="n">
-        <v>8.856987459432805</v>
+        <v>3.629257189712154</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC76" t="n">
-        <v>8.856987512479508</v>
+        <v>3.629257242758856</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC77" t="n">
-        <v>8.856987459432805</v>
+        <v>3.629257189712154</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.1697952168820188</v>
       </c>
       <c r="JC78" t="n">
-        <v>8.856987459432805</v>
+        <v>3.629257189712154</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>2.791318200473973</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC79" t="n">
-        <v>8.856987277558396</v>
+        <v>3.629257007837745</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.791318200473973</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC80" t="n">
-        <v>8.856987444276605</v>
+        <v>3.629257174555953</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4867320633075706</v>
+        <v>0.3697952168820188</v>
       </c>
       <c r="JC81" t="n">
-        <v>8.856987641307214</v>
+        <v>3.629257371586563</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4867320633075706</v>
+        <v>0.3697952168820188</v>
       </c>
       <c r="JC82" t="n">
-        <v>8.856987482167106</v>
+        <v>3.629257212446455</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.791318200473973</v>
+        <v>0.3697952168820188</v>
       </c>
       <c r="JC83" t="n">
-        <v>8.856987520057608</v>
+        <v>3.629257250336956</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4867320633075706</v>
+        <v>0.3697952168820188</v>
       </c>
       <c r="JC84" t="n">
-        <v>8.856987717088218</v>
+        <v>3.629257447367567</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC85" t="n">
-        <v>8.856987694353917</v>
+        <v>3.629257424633265</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC86" t="n">
-        <v>8.856987542791909</v>
+        <v>3.629257273071258</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC87" t="n">
-        <v>8.856987467010907</v>
+        <v>3.629257197290254</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.1697952168820188</v>
       </c>
       <c r="JC88" t="n">
-        <v>8.856987565526209</v>
+        <v>3.62925729580556</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.791318200473973</v>
+        <v>0.1697952168820188</v>
       </c>
       <c r="JC89" t="n">
-        <v>8.856987573104311</v>
+        <v>3.629257303383659</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.4867320633075706</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC90" t="n">
-        <v>8.856987838337824</v>
+        <v>3.629257568617173</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.791318200473973</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC91" t="n">
-        <v>8.856987542791909</v>
+        <v>3.629257273071258</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.791318200473973</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC92" t="n">
-        <v>8.856987785291123</v>
+        <v>3.62925751557047</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4867320633075706</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC93" t="n">
-        <v>8.856987868650226</v>
+        <v>3.629257598929575</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.791318200473973</v>
+        <v>0.3697952168820188</v>
       </c>
       <c r="JC94" t="n">
-        <v>8.856987701932017</v>
+        <v>3.629257432211367</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.3697952168820188</v>
       </c>
       <c r="JC95" t="n">
-        <v>8.856987891384527</v>
+        <v>3.629257621663876</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC96" t="n">
-        <v>8.856987542791909</v>
+        <v>3.629257273071258</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC97" t="n">
-        <v>8.856987338183199</v>
+        <v>3.629257068462547</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC98" t="n">
-        <v>8.856987451854703</v>
+        <v>3.629257182134053</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC99" t="n">
-        <v>8.856987467010907</v>
+        <v>3.629257197290254</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC100" t="n">
-        <v>8.856987232089793</v>
+        <v>3.629256962369142</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC101" t="n">
-        <v>8.856987292714596</v>
+        <v>3.629257022993944</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.1697952168820188</v>
       </c>
       <c r="JC102" t="n">
-        <v>8.85698716388689</v>
+        <v>3.629256894166238</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.791318200473973</v>
+        <v>0.3697952168820189</v>
       </c>
       <c r="JC103" t="n">
-        <v>8.856987300292698</v>
+        <v>3.629257030572046</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.4867320633075706</v>
+        <v>0.3697952168820189</v>
       </c>
       <c r="JC104" t="n">
-        <v>8.856987474589005</v>
+        <v>3.629257204868354</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-0.3794734148394769</v>
       </c>
       <c r="JC105" t="n">
-        <v>8.856987618572914</v>
+        <v>3.629257348852262</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.3794734148394769</v>
       </c>
       <c r="JC106" t="n">
-        <v>8.856987451854703</v>
+        <v>3.629257182134053</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC107" t="n">
-        <v>8.856987444276605</v>
+        <v>3.629257174555953</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.1697952168820188</v>
       </c>
       <c r="JC108" t="n">
-        <v>8.856987156308788</v>
+        <v>3.629256886588137</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.791318200473973</v>
+        <v>0.3697952168820188</v>
       </c>
       <c r="JC109" t="n">
-        <v>8.856987171464988</v>
+        <v>3.629256901744339</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4867320633075706</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC110" t="n">
-        <v>8.856987398808002</v>
+        <v>3.629257129087351</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.791318200473973</v>
+        <v>0.3697952168820188</v>
       </c>
       <c r="JC111" t="n">
-        <v>8.8569873836518</v>
+        <v>3.629257113931149</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4867320633075706</v>
+        <v>0.3697952168820188</v>
       </c>
       <c r="JC112" t="n">
-        <v>8.856987489745206</v>
+        <v>3.629257220024555</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4867320633075706</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC113" t="n">
-        <v>8.856987216933591</v>
+        <v>3.629256947212941</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC114" t="n">
-        <v>8.856987315448897</v>
+        <v>3.629257045728246</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC115" t="n">
-        <v>8.856987467010907</v>
+        <v>3.629257197290254</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC116" t="n">
-        <v>8.856987482167106</v>
+        <v>3.629257212446455</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC117" t="n">
-        <v>8.856987459432805</v>
+        <v>3.629257189712154</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC118" t="n">
-        <v>8.856987542791909</v>
+        <v>3.629257273071258</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC119" t="n">
-        <v>8.856987641307214</v>
+        <v>3.629257371586563</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC120" t="n">
-        <v>8.856987474589005</v>
+        <v>3.629257204868354</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC121" t="n">
-        <v>8.856987459432805</v>
+        <v>3.629257189712154</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC122" t="n">
-        <v>8.856987429120403</v>
+        <v>3.629257159399752</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC123" t="n">
-        <v>8.856987413964202</v>
+        <v>3.629257144243551</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC124" t="n">
-        <v>8.856987451854703</v>
+        <v>3.629257182134053</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC125" t="n">
-        <v>8.856987467010907</v>
+        <v>3.629257197290254</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.579473414839477</v>
       </c>
       <c r="JC126" t="n">
-        <v>8.856987459432805</v>
+        <v>3.629257189712154</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_2_000007.xlsx
+++ b/out/MLP-Mamba1_repeat_2_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4424398839473724</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.579473414839477</v>
+        <v>-1</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4573602974414825</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.7899999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4422866106033325</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.4288004636764526</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4702779352664948</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4390575885772705</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.423417717218399</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4079446494579315</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4497169852256775</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4219284653663635</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4234452545642853</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4157731831073761</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4624773263931274</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.3988533914089203</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.4115687906742096</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.579473414839477</v>
+        <v>0.16</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4213616549968719</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4592252671718597</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.579473414839477</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.413872092962265</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.579473414839477</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4401999115943909</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.3697952168820189</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.5120788216590881</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.119063848603515</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.5269427895545959</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.868332480325011</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.5536057353019714</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.119063848603515</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4254456162452698</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.3697952168820188</v>
+        <v>0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4374955892562866</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3794734148394769</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4286201000213623</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4097454249858856</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.3969566524028778</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.1697952168820188</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.5163130164146423</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.1697952168820188</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4155352413654327</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.1697952168820188</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4265040457248688</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4138708710670471</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.3640994131565094</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4366213977336884</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.579473414839477</v>
+        <v>0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.444168746471405</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.1697952168820188</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.5335900783538818</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.119063848603515</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.6640581488609314</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.119063848603515</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4766273498535156</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.119063848603515</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.5306364297866821</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.3697952168820188</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001281998857655562</v>
+        <v>-0.0001442297056872631</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.477955268127638</v>
+        <v>1.662755492955732</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.4025167226791382</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.3697952168820188</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>2.958195339930513</v>
+        <v>3.328081305828174</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.2216260079729183</v>
+        <v>0.2493376033478721</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>0.4717990458011627</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.579473414839477</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.921508316968085</v>
+        <v>2.161769372984634</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.2771045656649296</v>
+        <v>0.3117531333942921</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>0.4673292636871338</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.1697952168820188</v>
+        <v>-0.16</v>
       </c>
       <c r="JC42" t="n">
-        <v>2.254126749657094</v>
+        <v>2.535977632975608</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.397228080739525</v>
+        <v>0.446896638262141</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.5966265201568604</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.9190638486035146</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>2.771634940029304</v>
+        <v>3.118193712197221</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.4249553635384409</v>
+        <v>0.4780908817504419</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.6708008646965027</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.868332480325011</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>3.224347574305252</v>
+        <v>3.627512157246003</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4503677693768257</v>
+        <v>0.5066799709751724</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.6541286110877991</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.868332480325011</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>3.700159209821334</v>
+        <v>4.162817394577987</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2032425980310988</v>
+        <v>0.2286545814118022</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.6126130819320679</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.119063848603515</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>3.655902382679664</v>
+        <v>4.113026870119093</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.09815688533281568</v>
+        <v>0.110429711811827</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.4648372828960419</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.3697952168820189</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>3.648814185345555</v>
+        <v>4.105052370426346</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.0467688335445853</v>
+        <v>0.05261708287207957</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.3339449763298035</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.1697952168820188</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>3.644117016926645</v>
+        <v>4.099767840511219</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0138565178037387</v>
+        <v>0.01558948000753997</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.5399438142776489</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.9190638486035146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.625012162686346</v>
+        <v>4.078274628887007</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.009163384353095005</v>
+        <v>0.01031015333330494</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.5056878924369812</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.9190638486035146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>3.629477587058327</v>
+        <v>4.083299178444027</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.004687481955047708</v>
+        <v>0.005274903160156426</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.3519049882888794</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.1697952168820188</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>3.62968373661017</v>
+        <v>4.083531734850594</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002395889197842687</v>
+        <v>0.002695874514805839</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.4054586887359619</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.629784257088705</v>
+        <v>4.083645439858524</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0008972068212821196</v>
+        <v>0.001009982673942385</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.4476647078990936</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.629181719951207</v>
+        <v>4.082968241838502</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004867035624461271</v>
+        <v>0.0005485790107405222</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.4464428722858429</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.1697952168820188</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.629257485863503</v>
+        <v>4.083054094460991</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002318295252663819</v>
+        <v>0.00026123453343704</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.5139686465263367</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.1697952168820189</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.629234100123648</v>
+        <v>4.083028429691553</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.000141609312497821</v>
+        <v>0.0001603044597290868</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4780004620552063</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.3697952168820189</v>
+        <v>0.3</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.629285567931942</v>
+        <v>4.083086884481966</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>7.220268681140886e-05</v>
+        <v>8.146700922877794e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.3645827174186707</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.1697952168820188</v>
+        <v>0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.629287294285075</v>
+        <v>4.083089417997475</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>3.196644583905158e-05</v>
+        <v>3.696191149297746e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.7611038684844971</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.1697952168820187</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.629279975858463</v>
+        <v>4.083081820678642</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.930378117749152e-05</v>
+        <v>2.186207393301694e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>0.4644609093666077</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.3697952168820188</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.629285601168426</v>
+        <v>4.083088564442286</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>5.490501498730158e-06</v>
+        <v>6.65611277636684e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.37579146027565</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.629278428664165</v>
+        <v>4.083081163178829</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.4912258088588715</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.629272058343612</v>
+        <v>4.083074656452469</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-2.77474353817759e-06</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.3549853563308716</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.629267472434079</v>
+        <v>4.083070152549514</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.3990371227264404</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.1697952168820188</v>
+        <v>-0.3</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.629262039302611</v>
+        <v>4.083064719418045</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.6311620473861694</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.119063848603515</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.629256992681543</v>
+        <v>4.083059672796978</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.7955697178840637</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.868332480325011</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.62925731096176</v>
+        <v>4.083059991077194</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.8546670079231262</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.119063848603515</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.629258402208217</v>
+        <v>4.083061082323651</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>0.4881902933120728</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.3697952168820188</v>
+        <v>0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.62925771260108</v>
+        <v>4.083060392716515</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.4200476109981537</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.3697952168820188</v>
+        <v>0.16</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.629257742913483</v>
+        <v>4.083060423028917</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.5880451202392578</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.119063848603515</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.629257553460973</v>
+        <v>4.083060233576407</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.5280860662460327</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.119063848603515</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.629257606507676</v>
+        <v>4.08306028662311</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.399142861366272</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.3697952168820188</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.629257659554378</v>
+        <v>4.083060339669813</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.3960141539573669</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.629257621663876</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.3673733174800873</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.629257492836169</v>
+        <v>4.083060172951603</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.3768199682235718</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.629257348852262</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4340800046920776</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.629257189712154</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.4175062477588654</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.629257242758856</v>
+        <v>4.08305992287429</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.4064509868621826</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.629257189712154</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.3390747904777527</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.1697952168820188</v>
+        <v>0.16</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.629257189712154</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.5724238157272339</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.119063848603515</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.629257007837745</v>
+        <v>4.083059687953178</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.5688772201538086</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.119063848603515</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.629257174555953</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.3315207064151764</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.3697952168820188</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.629257371586563</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.4277754724025726</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.3697952168820188</v>
+        <v>0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.629257212446455</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.5466787815093994</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.3697952168820188</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.629257250336956</v>
+        <v>4.08305993045239</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4789655208587646</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.3697952168820188</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.629257447367567</v>
+        <v>4.083060127483001</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.3694081604480743</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.629257424633265</v>
+        <v>4.0830601047487</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.4072338342666626</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.629257273071258</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.4662511944770813</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.629257197290254</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.4383299648761749</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.1697952168820188</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.62925729580556</v>
+        <v>4.083059975920994</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.5417588949203491</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.1697952168820188</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.629257303383659</v>
+        <v>4.083059983499094</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.4138253033161163</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.119063848603515</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.629257568617173</v>
+        <v>4.083060248732608</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.5252978205680847</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.119063848603515</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.629257273071258</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.5555630922317505</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.119063848603515</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.62925751557047</v>
+        <v>4.083060195685905</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3197940587997437</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.119063848603515</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.629257598929575</v>
+        <v>4.083060279045009</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.6616989970207214</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.3697952168820188</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.629257432211367</v>
+        <v>4.083060112326801</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.3335032165050507</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.3697952168820188</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.629257621663876</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.3943578898906708</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.629257273071258</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.3983265161514282</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.629257068462547</v>
+        <v>4.083059748577981</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.4237519204616547</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.629257182134053</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.3103587329387665</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.629257197290254</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.4304302036762238</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.629256962369142</v>
+        <v>4.083059642484576</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.3093695640563965</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.579473414839477</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.629257022993944</v>
+        <v>4.083059703109379</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.4554633796215057</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.1697952168820188</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.629256894166238</v>
+        <v>4.083059574281672</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.6210371851921082</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.3697952168820189</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.629257030572046</v>
+        <v>4.08305971068748</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.4711235761642456</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.3697952168820189</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.629257204868354</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.3347855508327484</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3794734148394769</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.629257348852262</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.448776513338089</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3794734148394769</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.629257182134053</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.2557652294635773</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.579473414839477</v>
+        <v>0.16</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.629257174555953</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3773356676101685</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.1697952168820188</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.629256886588137</v>
+        <v>4.083059566703572</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.5273855924606323</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.3697952168820188</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.629256901744339</v>
+        <v>4.083059581859773</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3787193596363068</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.119063848603515</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.629257129087351</v>
+        <v>4.083059809202784</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.5175524950027466</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.3697952168820188</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.629257113931149</v>
+        <v>4.083059794046584</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.2425142526626587</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.3697952168820188</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.629257220024555</v>
+        <v>4.08305990013999</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3940127789974213</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.629256947212941</v>
+        <v>4.083059627328375</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.4976829886436462</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.629257045728246</v>
+        <v>4.08305972584368</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.4168989360332489</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.629257197290254</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4250018894672394</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.579473414839477</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.629257212446455</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.439544677734375</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.579473414839477</v>
+        <v>0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.629257189712154</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.4772178530693054</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.579473414839477</v>
+        <v>0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.629257273071258</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.3665090501308441</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.579473414839477</v>
+        <v>0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.629257371586563</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.3294552564620972</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.629257204868354</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.4045306444168091</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.629257189712154</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.379700779914856</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.629257159399752</v>
+        <v>4.083059839515186</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.4371638596057892</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.629257144243551</v>
+        <v>4.083059824358986</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.4013687968254089</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.629257182134053</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.4087414145469666</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.579473414839477</v>
+        <v>-0.4399999999999998</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.629257197290254</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4102735817432404</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.579473414839477</v>
+        <v>0.3000000000000002</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.629257189712154</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_2_000007.xlsx
+++ b/out/MLP-Mamba1_repeat_2_000007.xlsx
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.4288004636764526</v>
+        <v>0.428800493478775</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.5799999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.4157731831073761</v>
+        <v>0.4157731235027313</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.7199999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.4213616549968719</v>
+        <v>0.4213616251945496</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.1199999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.413872092962265</v>
+        <v>0.4138720035552979</v>
       </c>
       <c r="JB19" t="n">
         <v>0.4399999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.4401999115943909</v>
+        <v>0.4401998519897461</v>
       </c>
       <c r="JB20" t="n">
         <v>0.7199999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.4286201000213623</v>
+        <v>0.4286200702190399</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.9999999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.3969566524028778</v>
+        <v>0.3969566226005554</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.7199999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.3640994131565094</v>
+        <v>0.364099383354187</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.5799999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.4366213977336884</v>
+        <v>0.436621367931366</v>
       </c>
       <c r="JB34" t="n">
         <v>0.3</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.4766273498535156</v>
+        <v>0.4766274094581604</v>
       </c>
       <c r="JB38" t="n">
         <v>0.7199999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.5306364297866821</v>
+        <v>0.5306364893913269</v>
       </c>
       <c r="JB39" t="n">
         <v>0.5799999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.4673292636871338</v>
+        <v>0.4673293232917786</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.16</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.6126130819320679</v>
+        <v>0.6126131415367126</v>
       </c>
       <c r="JB46" t="n">
         <v>0.4399999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.3339449763298035</v>
+        <v>0.3339449167251587</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.4399999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.5056878924369812</v>
+        <v>0.5056878328323364</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.7199999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.3519049882888794</v>
+        <v>0.3519050478935242</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.7199999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.4464428722858429</v>
+        <v>0.4464429616928101</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.5799999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.5139686465263367</v>
+        <v>0.5139687061309814</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.5799999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.3645827174186707</v>
+        <v>0.3645827770233154</v>
       </c>
       <c r="JB57" t="n">
         <v>0.3</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.37579146027565</v>
+        <v>0.3757914304733276</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.5799999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.8546670079231262</v>
+        <v>0.8546668291091919</v>
       </c>
       <c r="JB66" t="n">
         <v>0.4399999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.4200476109981537</v>
+        <v>0.4200475811958313</v>
       </c>
       <c r="JB68" t="n">
         <v>0.16</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.5880451202392578</v>
+        <v>0.588045060634613</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.7199999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.5280860662460327</v>
+        <v>0.5280860066413879</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.7199999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.399142861366272</v>
+        <v>0.3991428017616272</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.7199999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.3960141539573669</v>
+        <v>0.3960141241550446</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.8599999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.3768199682235718</v>
+        <v>0.3768199384212494</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.4064509868621826</v>
+        <v>0.4064510464668274</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.7199999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.3390747904777527</v>
+        <v>0.3390748798847198</v>
       </c>
       <c r="JB78" t="n">
         <v>0.16</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.5688772201538086</v>
+        <v>0.5688771605491638</v>
       </c>
       <c r="JB80" t="n">
         <v>0.1600000000000001</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.3315207064151764</v>
+        <v>0.3315207958221436</v>
       </c>
       <c r="JB81" t="n">
         <v>0.4399999999999999</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.4277754724025726</v>
+        <v>0.4277755320072174</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="JC82" t="n">
         <v>4.083059892561889</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.5466787815093994</v>
+        <v>0.5466787219047546</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
         <v>4.08305993045239</v>
@@ -67724,7 +67724,7 @@
         <v>0.4789655208587646</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
         <v>4.083060127483001</v>
@@ -68519,7 +68519,7 @@
         <v>0.3694081604480743</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>4.0830601047487</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.4072338342666626</v>
+        <v>0.4072338938713074</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>4.083059953186692</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.5417588949203491</v>
+        <v>0.5417588353157043</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.4399999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.4138253033161163</v>
+        <v>0.4138252139091492</v>
       </c>
       <c r="JB90" t="n">
         <v>0.4399999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.5252978205680847</v>
+        <v>0.5252977609634399</v>
       </c>
       <c r="JB91" t="n">
         <v>0.4399999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.3197940587997437</v>
+        <v>0.3197940289974213</v>
       </c>
       <c r="JB93" t="n">
         <v>0.4399999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.3335032165050507</v>
+        <v>0.3335031867027283</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.1199999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.3943578898906708</v>
+        <v>0.394357830286026</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.7199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.3983265161514282</v>
+        <v>0.398326575756073</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.9999999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.3103587329387665</v>
+        <v>0.3103588223457336</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.8599999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.4304302036762238</v>
+        <v>0.4304302632808685</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.5799999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.3093695640563965</v>
+        <v>0.3093695938587189</v>
       </c>
       <c r="JB101" t="n">
         <v>0.3</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.3347855508327484</v>
+        <v>0.3347856104373932</v>
       </c>
       <c r="JB105" t="n">
         <v>0.4399999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.448776513338089</v>
+        <v>0.4487764239311218</v>
       </c>
       <c r="JB106" t="n">
         <v>0.1600000000000001</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.2557652294635773</v>
+        <v>0.2557653188705444</v>
       </c>
       <c r="JB107" t="n">
         <v>0.16</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.5273855924606323</v>
+        <v>0.5273856520652771</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.4399999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.3787193596363068</v>
+        <v>0.3787194192409515</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.4399999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.5175524950027466</v>
+        <v>0.5175524353981018</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.4399999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.2425142526626587</v>
+        <v>0.2425142824649811</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.5799999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.3940127789974213</v>
+        <v>0.3940128684043884</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.5799999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.4976829886436462</v>
+        <v>0.4976831078529358</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.7199999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.4168989360332489</v>
+        <v>0.4168989956378937</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.4399999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.4250018894672394</v>
+        <v>0.4250019490718842</v>
       </c>
       <c r="JB116" t="n">
         <v>0.4399999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.439544677734375</v>
+        <v>0.4395447075366974</v>
       </c>
       <c r="JB117" t="n">
         <v>0.3</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.4772178530693054</v>
+        <v>0.4772177934646606</v>
       </c>
       <c r="JB118" t="n">
         <v>0.3</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.3294552564620972</v>
+        <v>0.3294552862644196</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.7199999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.4045306444168091</v>
+        <v>0.4045307338237762</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.8599999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.379700779914856</v>
+        <v>0.3797008693218231</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.8599999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.4013687968254089</v>
+        <v>0.4013688862323761</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.5799999999999998</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.4087414145469666</v>
+        <v>0.4087414741516113</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.4399999999999998</v>
